--- a/RefractionApp/Refraction/Resources/SampleData/drug_treatment.xlsx
+++ b/RefractionApp/Refraction/Resources/SampleData/drug_treatment.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,90 +435,90 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.83</v>
+        <v>4.5</v>
       </c>
       <c r="B2" t="n">
-        <v>8.24</v>
+        <v>7.2</v>
       </c>
       <c r="C2" t="n">
-        <v>11.78</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.84</v>
+        <v>5.1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.31</v>
+        <v>8.1</v>
       </c>
       <c r="C3" t="n">
-        <v>9.01</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="B4" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="C4" t="n">
-        <v>11.57</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5.14</v>
+        <v>5.3</v>
       </c>
       <c r="B5" t="n">
-        <v>8.85</v>
+        <v>8.5</v>
       </c>
       <c r="C5" t="n">
-        <v>14.33</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5.79</v>
+        <v>4.9</v>
       </c>
       <c r="B6" t="n">
-        <v>8.67</v>
+        <v>7.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.52</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.78</v>
+        <v>5.2</v>
       </c>
       <c r="B7" t="n">
-        <v>8.869999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>14.62</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.34</v>
+        <v>7.9</v>
       </c>
       <c r="C8" t="n">
-        <v>13.06</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3.26</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>8.029999999999999</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.98</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
